--- a/data/database.xlsx
+++ b/data/database.xlsx
@@ -10575,7 +10575,7 @@
         <v>615</v>
       </c>
       <c r="H89" s="6" t="s">
-        <v>616</v>
+        <v>1973</v>
       </c>
       <c r="I89" s="6" t="s">
         <v>617</v>
@@ -10593,7 +10593,7 @@
         <v>392</v>
       </c>
       <c r="P89" s="6" t="s">
-        <v>39</v>
+        <v>1966</v>
       </c>
       <c r="Q89" s="7" t="s">
         <v>618</v>
